--- a/output/Hubei/十堰市_news.xlsx
+++ b/output/Hubei/十堰市_news.xlsx
@@ -135,7 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,22 +153,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -620,152 +613,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -775,7 +768,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1217,12 +1211,8 @@
       <c r="L2">
         <v>338</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
+      <c r="M2"/>
+      <c r="N2"/>
       <c r="O2" s="5" t="s">
         <v>23</v>
       </c>
@@ -1267,13 +1257,9 @@
       <c r="L3">
         <v>19</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3" s="6" t="s">
         <v>30</v>
       </c>
       <c r="P3" t="s">
